--- a/Data/Hires/testDataRomania - Copy (2).xlsx
+++ b/Data/Hires/testDataRomania - Copy (2).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{4D10E8C5-917B-456D-8788-C76911491127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F83A02-BA08-4D82-BDC8-3F1ADD769421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,7 +11,6 @@
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1604,7 +1603,7 @@
       </c>
       <c r="K2" s="14">
         <f ca="1">TODAY()-100</f>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L2" s="11" t="s">
         <v>81</v>
@@ -1641,7 +1640,7 @@
       </c>
       <c r="W2" s="14">
         <f ca="1">TODAY()-100</f>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X2" s="13" t="s">
         <v>92</v>
@@ -1711,7 +1710,7 @@
       </c>
       <c r="AT2" s="14" t="str">
         <f t="shared" ref="AT2:AT16" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU2" s="11" t="s">
         <v>100</v>
@@ -1727,11 +1726,11 @@
       </c>
       <c r="AY2" s="14">
         <f ca="1">TODAY()-100</f>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ2" s="14">
         <f ca="1">TODAY()-100</f>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA2" s="23" t="s">
         <v>100</v>
@@ -1759,7 +1758,7 @@
       </c>
       <c r="BI2" s="1">
         <f t="array" aca="1" ref="BI2:BI16" ca="1">_xlfn.RANDARRAY(15,1,123456,999999,TRUE)</f>
-        <v>279611</v>
+        <v>238284</v>
       </c>
       <c r="BJ2" s="16" t="s">
         <v>114</v>
@@ -1858,7 +1857,7 @@
       </c>
       <c r="K3" s="14">
         <f t="shared" ref="K3:K16" ca="1" si="1">TODAY()-100</f>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L3" s="28" t="s">
         <v>81</v>
@@ -1895,7 +1894,7 @@
       </c>
       <c r="W3" s="14">
         <f t="shared" ref="W3:W16" ca="1" si="2">TODAY()-100</f>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X3" s="13" t="s">
         <v>92</v>
@@ -1929,7 +1928,7 @@
       </c>
       <c r="AH3" s="14">
         <f ca="1">TODAY()+200</f>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="AI3" s="13" t="s">
         <v>101</v>
@@ -1966,7 +1965,7 @@
       </c>
       <c r="AT3" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU3" s="11" t="s">
         <v>100</v>
@@ -1982,15 +1981,15 @@
       </c>
       <c r="AY3" s="14">
         <f t="shared" ref="AY3:AZ16" ca="1" si="3">TODAY()-100</f>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ3" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA3" s="14">
         <f ca="1">TODAY()+200</f>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="BB3" s="27" t="s">
         <v>81</v>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="BI3" s="31">
         <f ca="1"/>
-        <v>412211</v>
+        <v>246173</v>
       </c>
       <c r="BJ3" s="16" t="s">
         <v>114</v>
@@ -2114,7 +2113,7 @@
       </c>
       <c r="K4" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L4" s="11" t="s">
         <v>81</v>
@@ -2151,7 +2150,7 @@
       </c>
       <c r="W4" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X4" s="13" t="s">
         <v>92</v>
@@ -2185,7 +2184,7 @@
       </c>
       <c r="AH4" s="14">
         <f t="shared" ref="AH4:AH13" ca="1" si="4">TODAY()+200</f>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="AI4" s="13" t="s">
         <v>101</v>
@@ -2222,7 +2221,7 @@
       </c>
       <c r="AT4" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU4" s="11" t="s">
         <v>100</v>
@@ -2238,15 +2237,15 @@
       </c>
       <c r="AY4" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ4" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA4" s="14">
         <f t="shared" ref="BA4:BA13" ca="1" si="5">TODAY()+200</f>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="BB4" s="27" t="s">
         <v>81</v>
@@ -2271,7 +2270,7 @@
       </c>
       <c r="BI4" s="31">
         <f ca="1"/>
-        <v>310571</v>
+        <v>283887</v>
       </c>
       <c r="BJ4" s="16" t="s">
         <v>114</v>
@@ -2370,7 +2369,7 @@
       </c>
       <c r="K5" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L5" s="28" t="s">
         <v>81</v>
@@ -2407,7 +2406,7 @@
       </c>
       <c r="W5" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X5" s="13" t="s">
         <v>92</v>
@@ -2441,7 +2440,7 @@
       </c>
       <c r="AH5" s="14">
         <f t="shared" ca="1" si="4"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="AI5" s="13" t="s">
         <v>101</v>
@@ -2478,7 +2477,7 @@
       </c>
       <c r="AT5" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU5" s="11" t="s">
         <v>100</v>
@@ -2494,15 +2493,15 @@
       </c>
       <c r="AY5" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ5" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA5" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="BB5" s="27" t="s">
         <v>81</v>
@@ -2527,7 +2526,7 @@
       </c>
       <c r="BI5" s="31">
         <f ca="1"/>
-        <v>465794</v>
+        <v>750818</v>
       </c>
       <c r="BJ5" s="16" t="s">
         <v>114</v>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="K6" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>81</v>
@@ -2663,7 +2662,7 @@
       </c>
       <c r="W6" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X6" s="13" t="s">
         <v>92</v>
@@ -2733,7 +2732,7 @@
       </c>
       <c r="AT6" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU6" s="11" t="s">
         <v>100</v>
@@ -2749,11 +2748,11 @@
       </c>
       <c r="AY6" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ6" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA6" s="23" t="str">
         <f t="shared" ref="BA6:BA15" si="6">AH6</f>
@@ -2782,7 +2781,7 @@
       </c>
       <c r="BI6" s="31">
         <f ca="1"/>
-        <v>747059</v>
+        <v>646828</v>
       </c>
       <c r="BJ6" s="16" t="s">
         <v>114</v>
@@ -2881,7 +2880,7 @@
       </c>
       <c r="K7" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L7" s="28" t="s">
         <v>81</v>
@@ -2918,7 +2917,7 @@
       </c>
       <c r="W7" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X7" s="13" t="s">
         <v>92</v>
@@ -2952,7 +2951,7 @@
       </c>
       <c r="AH7" s="14">
         <f t="shared" ca="1" si="4"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="AI7" s="13" t="s">
         <v>101</v>
@@ -2989,7 +2988,7 @@
       </c>
       <c r="AT7" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU7" s="11" t="s">
         <v>100</v>
@@ -3005,15 +3004,15 @@
       </c>
       <c r="AY7" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ7" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA7" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="BB7" s="27" t="s">
         <v>81</v>
@@ -3038,7 +3037,7 @@
       </c>
       <c r="BI7" s="31">
         <f ca="1"/>
-        <v>509816</v>
+        <v>693236</v>
       </c>
       <c r="BJ7" s="16" t="s">
         <v>114</v>
@@ -3137,7 +3136,7 @@
       </c>
       <c r="K8" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L8" s="11" t="s">
         <v>81</v>
@@ -3174,7 +3173,7 @@
       </c>
       <c r="W8" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X8" s="13" t="s">
         <v>92</v>
@@ -3244,7 +3243,7 @@
       </c>
       <c r="AT8" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU8" s="11" t="s">
         <v>100</v>
@@ -3260,11 +3259,11 @@
       </c>
       <c r="AY8" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ8" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA8" s="23" t="str">
         <f t="shared" si="6"/>
@@ -3293,7 +3292,7 @@
       </c>
       <c r="BI8" s="31">
         <f ca="1"/>
-        <v>467081</v>
+        <v>978481</v>
       </c>
       <c r="BJ8" s="16" t="s">
         <v>114</v>
@@ -3392,7 +3391,7 @@
       </c>
       <c r="K9" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L9" s="28" t="s">
         <v>81</v>
@@ -3429,7 +3428,7 @@
       </c>
       <c r="W9" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X9" s="13" t="s">
         <v>92</v>
@@ -3463,7 +3462,7 @@
       </c>
       <c r="AH9" s="14">
         <f t="shared" ca="1" si="4"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="AI9" s="13" t="s">
         <v>101</v>
@@ -3500,7 +3499,7 @@
       </c>
       <c r="AT9" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU9" s="11" t="s">
         <v>100</v>
@@ -3516,15 +3515,15 @@
       </c>
       <c r="AY9" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ9" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA9" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="BB9" s="27" t="s">
         <v>81</v>
@@ -3549,7 +3548,7 @@
       </c>
       <c r="BI9" s="31">
         <f ca="1"/>
-        <v>334939</v>
+        <v>574877</v>
       </c>
       <c r="BJ9" s="16" t="s">
         <v>114</v>
@@ -3648,7 +3647,7 @@
       </c>
       <c r="K10" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>81</v>
@@ -3685,7 +3684,7 @@
       </c>
       <c r="W10" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X10" s="13" t="s">
         <v>92</v>
@@ -3755,7 +3754,7 @@
       </c>
       <c r="AT10" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU10" s="11" t="s">
         <v>100</v>
@@ -3771,11 +3770,11 @@
       </c>
       <c r="AY10" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ10" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA10" s="39" t="str">
         <f t="shared" si="6"/>
@@ -3804,7 +3803,7 @@
       </c>
       <c r="BI10" s="31">
         <f ca="1"/>
-        <v>244907</v>
+        <v>871691</v>
       </c>
       <c r="BJ10" s="16" t="s">
         <v>114</v>
@@ -3903,7 +3902,7 @@
       </c>
       <c r="K11" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L11" s="28" t="s">
         <v>81</v>
@@ -3940,7 +3939,7 @@
       </c>
       <c r="W11" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X11" s="13" t="s">
         <v>92</v>
@@ -3974,7 +3973,7 @@
       </c>
       <c r="AH11" s="14">
         <f t="shared" ca="1" si="4"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="AI11" s="13" t="s">
         <v>101</v>
@@ -4011,7 +4010,7 @@
       </c>
       <c r="AT11" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU11" s="11" t="s">
         <v>100</v>
@@ -4027,15 +4026,15 @@
       </c>
       <c r="AY11" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ11" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA11" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="BB11" s="27" t="s">
         <v>81</v>
@@ -4060,7 +4059,7 @@
       </c>
       <c r="BI11" s="31">
         <f ca="1"/>
-        <v>907542</v>
+        <v>292286</v>
       </c>
       <c r="BJ11" s="16" t="s">
         <v>114</v>
@@ -4159,7 +4158,7 @@
       </c>
       <c r="K12" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L12" s="11" t="s">
         <v>81</v>
@@ -4196,7 +4195,7 @@
       </c>
       <c r="W12" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X12" s="13" t="s">
         <v>92</v>
@@ -4266,7 +4265,7 @@
       </c>
       <c r="AT12" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU12" s="11" t="s">
         <v>100</v>
@@ -4282,11 +4281,11 @@
       </c>
       <c r="AY12" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ12" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA12" s="39" t="str">
         <f t="shared" si="6"/>
@@ -4315,7 +4314,7 @@
       </c>
       <c r="BI12" s="31">
         <f ca="1"/>
-        <v>313148</v>
+        <v>942753</v>
       </c>
       <c r="BJ12" s="16" t="s">
         <v>114</v>
@@ -4414,7 +4413,7 @@
       </c>
       <c r="K13" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L13" s="28" t="s">
         <v>81</v>
@@ -4451,7 +4450,7 @@
       </c>
       <c r="W13" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X13" s="13" t="s">
         <v>92</v>
@@ -4485,7 +4484,7 @@
       </c>
       <c r="AH13" s="14">
         <f t="shared" ca="1" si="4"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="AI13" s="13" t="s">
         <v>101</v>
@@ -4522,7 +4521,7 @@
       </c>
       <c r="AT13" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU13" s="11" t="s">
         <v>100</v>
@@ -4538,15 +4537,15 @@
       </c>
       <c r="AY13" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ13" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA13" s="14">
         <f t="shared" ca="1" si="5"/>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="BB13" s="27" t="s">
         <v>81</v>
@@ -4571,7 +4570,7 @@
       </c>
       <c r="BI13" s="31">
         <f ca="1"/>
-        <v>807079</v>
+        <v>468720</v>
       </c>
       <c r="BJ13" s="16" t="s">
         <v>114</v>
@@ -4670,7 +4669,7 @@
       </c>
       <c r="K14" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L14" s="11" t="s">
         <v>81</v>
@@ -4707,7 +4706,7 @@
       </c>
       <c r="W14" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X14" s="13" t="s">
         <v>92</v>
@@ -4777,7 +4776,7 @@
       </c>
       <c r="AT14" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU14" s="11" t="s">
         <v>100</v>
@@ -4793,11 +4792,11 @@
       </c>
       <c r="AY14" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ14" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA14" s="39" t="str">
         <f t="shared" si="6"/>
@@ -4826,7 +4825,7 @@
       </c>
       <c r="BI14" s="31">
         <f ca="1"/>
-        <v>985323</v>
+        <v>150186</v>
       </c>
       <c r="BJ14" s="16" t="s">
         <v>114</v>
@@ -4925,7 +4924,7 @@
       </c>
       <c r="K15" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L15" s="28" t="s">
         <v>81</v>
@@ -4962,7 +4961,7 @@
       </c>
       <c r="W15" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X15" s="13" t="s">
         <v>92</v>
@@ -5032,7 +5031,7 @@
       </c>
       <c r="AT15" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU15" s="11" t="s">
         <v>100</v>
@@ -5048,11 +5047,11 @@
       </c>
       <c r="AY15" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ15" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA15" s="39" t="str">
         <f t="shared" si="6"/>
@@ -5081,7 +5080,7 @@
       </c>
       <c r="BI15" s="31">
         <f ca="1"/>
-        <v>979896</v>
+        <v>352157</v>
       </c>
       <c r="BJ15" s="16" t="s">
         <v>114</v>
@@ -5180,7 +5179,7 @@
       </c>
       <c r="K16" s="14">
         <f t="shared" ca="1" si="1"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="L16" s="11" t="s">
         <v>81</v>
@@ -5217,7 +5216,7 @@
       </c>
       <c r="W16" s="14">
         <f t="shared" ca="1" si="2"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="X16" s="13" t="s">
         <v>92</v>
@@ -5251,7 +5250,7 @@
       </c>
       <c r="AH16" s="14">
         <f t="shared" ref="AH16" ca="1" si="7">TODAY()+200</f>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="AI16" s="13" t="s">
         <v>101</v>
@@ -5288,7 +5287,7 @@
       </c>
       <c r="AT16" s="14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>30/07/2024</v>
+        <v>30/10/2024</v>
       </c>
       <c r="AU16" s="11" t="s">
         <v>100</v>
@@ -5304,15 +5303,15 @@
       </c>
       <c r="AY16" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="AZ16" s="14">
         <f t="shared" ca="1" si="3"/>
-        <v>45503</v>
+        <v>45595</v>
       </c>
       <c r="BA16" s="14">
         <f t="shared" ref="BA16" ca="1" si="8">TODAY()+200</f>
-        <v>45803</v>
+        <v>45895</v>
       </c>
       <c r="BB16" s="27" t="s">
         <v>81</v>
@@ -5337,7 +5336,7 @@
       </c>
       <c r="BI16" s="31">
         <f ca="1"/>
-        <v>911181</v>
+        <v>536202</v>
       </c>
       <c r="BJ16" s="16" t="s">
         <v>114</v>
